--- a/artfynd/A 18759-2026 artfynd.xlsx
+++ b/artfynd/A 18759-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103282179</v>
+        <v>103282234</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510361.8563326085</v>
+        <v>510337</v>
       </c>
       <c r="R2" t="n">
-        <v>6686668.837749682</v>
+        <v>6686649</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -766,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,37 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103281650</v>
+        <v>103281695</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510519.3410660959</v>
+        <v>510568</v>
       </c>
       <c r="R3" t="n">
-        <v>6686782.745435601</v>
+        <v>6686801</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,37 +905,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103281800</v>
+        <v>103282080</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510671.257316141</v>
+        <v>510484</v>
       </c>
       <c r="R4" t="n">
-        <v>6686761.388034509</v>
+        <v>6686790</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -992,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,15 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103282290</v>
+        <v>103281611</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,7 +1046,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -1075,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510332.5036217478</v>
+        <v>510500</v>
       </c>
       <c r="R5" t="n">
-        <v>6686694.517713862</v>
+        <v>6686756</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1113,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,15 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103282117</v>
+        <v>103281641</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1171,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1193,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510439.1743282081</v>
+        <v>510518</v>
       </c>
       <c r="R6" t="n">
-        <v>6686703.739829046</v>
+        <v>6686781</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1228,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,60 +1253,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103282234</v>
+        <v>103281650</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510337.1007069618</v>
+        <v>510519</v>
       </c>
       <c r="R7" t="n">
-        <v>6686648.453907334</v>
+        <v>6686782</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1350,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,43 +1366,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103281695</v>
+        <v>103281800</v>
       </c>
       <c r="B8" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1433,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510567.9232360575</v>
+        <v>510671</v>
       </c>
       <c r="R8" t="n">
-        <v>6686800.226222055</v>
+        <v>6686762</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1468,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,12 +1482,7 @@
         <v>103281985</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510541.0943445192</v>
+        <v>510541</v>
       </c>
       <c r="R9" t="n">
-        <v>6686811.0480004</v>
+        <v>6686811</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1623,15 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103281611</v>
+        <v>103282117</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,19 +1620,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1678,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510499.5667522592</v>
+        <v>510439</v>
       </c>
       <c r="R10" t="n">
-        <v>6686756.430241469</v>
+        <v>6686703</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1713,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1723,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,37 +1705,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103282080</v>
+        <v>103282179</v>
       </c>
       <c r="B11" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1796,10 +1746,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510483.0934546761</v>
+        <v>510361</v>
       </c>
       <c r="R11" t="n">
-        <v>6686790.072472672</v>
+        <v>6686668</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1831,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1841,7 +1791,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,6 +1815,119 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>103282290</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Borlänge, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>510333</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6686695</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
